--- a/artfynd/A 49817-2025 artfynd.xlsx
+++ b/artfynd/A 49817-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>71731238</v>
+        <v>122383795</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>100100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,23 +708,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Humsjön 140m öst om, Vrm</t>
+          <t>Finnfallet, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>381397.2060068876</v>
+        <v>381564</v>
       </c>
       <c r="R2" t="n">
-        <v>6632383.009992217</v>
+        <v>6632622</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,22 +756,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-06-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-06-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>upptäcks på håll. Kommer rakt mot mig. tappas bakom några björkar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,15 +781,123 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Alessandra Munari</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Vesa Jussila</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>71731238</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Humsjön 140m öst om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>381397</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6632383</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gräsmark</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2018-06-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2018-06-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Billy Lindblom</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Billy Lindblom</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
